--- a/17 18 20/Excel/6.Project/Inventory Managment/Raw Data/MSF.xlsx
+++ b/17 18 20/Excel/6.Project/Inventory Managment/Raw Data/MSF.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\Excel\Project\Raw Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\Excel\6.Project\Inventory Managment\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -420,46 +420,6 @@
         <name val="Candara"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Candara"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
@@ -785,6 +745,46 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Candara"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1167,16 +1167,16 @@
     <tableColumn id="6" name="Tour Date" dataDxfId="12"/>
     <tableColumn id="7" name="Tour Name" dataDxfId="11"/>
     <tableColumn id="8" name="Dept" dataDxfId="10"/>
-    <tableColumn id="20" name="Status-1" dataDxfId="0" dataCellStyle="Good"/>
-    <tableColumn id="26" name="Supplier" dataDxfId="9"/>
-    <tableColumn id="16" name="Hotel-1" dataDxfId="8"/>
-    <tableColumn id="15" name="Options" dataDxfId="7"/>
-    <tableColumn id="18" name="SGL" dataDxfId="6"/>
-    <tableColumn id="19" name="DBL" dataDxfId="5"/>
-    <tableColumn id="22" name="TPL" dataDxfId="4"/>
-    <tableColumn id="23" name="TOTAL" dataDxfId="3"/>
-    <tableColumn id="25" name="Operating" dataDxfId="2"/>
-    <tableColumn id="27" name="CtOF" dataDxfId="1">
+    <tableColumn id="20" name="Status-1" dataDxfId="9" dataCellStyle="Good"/>
+    <tableColumn id="26" name="Supplier" dataDxfId="8"/>
+    <tableColumn id="16" name="Hotel-1" dataDxfId="7"/>
+    <tableColumn id="15" name="Options" dataDxfId="6"/>
+    <tableColumn id="18" name="SGL" dataDxfId="5"/>
+    <tableColumn id="19" name="DBL" dataDxfId="4"/>
+    <tableColumn id="22" name="TPL" dataDxfId="3"/>
+    <tableColumn id="23" name="TOTAL" dataDxfId="2"/>
+    <tableColumn id="25" name="Operating" dataDxfId="1"/>
+    <tableColumn id="27" name="CtOF" dataDxfId="0">
       <calculatedColumnFormula>OR(ParMSF[[#This Row],[Status-1]]="XXLD",AND(ParMSF[[#This Row],[Status-1]]="CNFD",ParMSF[[#This Row],[Operating]]="OK"),ParMSF[[#This Row],[Status-1]]="RLSD",ParMSF[[#This Row],[Status-1]]="PNDG",ParMSF[[#This Row],[Status-1]]="")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
